--- a/115配課表.xlsx
+++ b/115配課表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD66096-B125-4D5F-B7BA-05D1F476A6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A98C4CE-4A7A-46E2-B516-77070A9A2101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7597B60B-03FC-42F6-A4B7-81E2EE8A7242}"/>
   </bookViews>
@@ -39,174 +39,183 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="51">
+  <si>
+    <t>導師</t>
+  </si>
+  <si>
+    <t>葉麗君</t>
+  </si>
+  <si>
+    <t>邱翊睿</t>
+  </si>
+  <si>
+    <t>林金旺</t>
+  </si>
+  <si>
+    <t>謝彩鳳</t>
+  </si>
+  <si>
+    <t>張文馨</t>
+  </si>
+  <si>
+    <t>鄧竹君</t>
+  </si>
+  <si>
+    <t>韓紫綾</t>
+  </si>
+  <si>
+    <t>江治峰</t>
+  </si>
+  <si>
+    <t>張素梅</t>
+  </si>
+  <si>
+    <t>王思元</t>
+  </si>
+  <si>
+    <t>周正軒</t>
+  </si>
+  <si>
+    <t>卓呈祈</t>
+  </si>
+  <si>
+    <t>林玉惠</t>
+  </si>
+  <si>
+    <t>沈士和</t>
+  </si>
+  <si>
+    <t>榮彩君</t>
+  </si>
+  <si>
+    <t>林玉萍</t>
+  </si>
+  <si>
+    <t>王勛瑤</t>
+  </si>
+  <si>
+    <t>鍾智宇</t>
+  </si>
+  <si>
+    <t>音樂</t>
+  </si>
+  <si>
+    <t>輔導</t>
+  </si>
+  <si>
+    <t>童軍</t>
+  </si>
+  <si>
+    <t>家政</t>
+  </si>
+  <si>
+    <t>健教</t>
+  </si>
+  <si>
+    <t>學校自治</t>
+  </si>
+  <si>
+    <t>農騰虎嘯</t>
+  </si>
+  <si>
+    <t>品味生活</t>
+  </si>
+  <si>
+    <t>體育</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱翊睿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>廖怡然</t>
+  </si>
+  <si>
+    <t>國文</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>數學</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>地理</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>公民</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活科技</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>視覺藝術</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>表演藝術</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>本土語</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>人文風光</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>社團活動</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>風馳電掣</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>全球化</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>資訊科技</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生物</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
   <si>
     <t>班級</t>
-  </si>
-  <si>
-    <t>導師</t>
-  </si>
-  <si>
-    <t>葉麗君</t>
-  </si>
-  <si>
-    <t>邱翊睿</t>
-  </si>
-  <si>
-    <t>林金旺</t>
-  </si>
-  <si>
-    <t>謝彩鳳</t>
-  </si>
-  <si>
-    <t>張文馨</t>
-  </si>
-  <si>
-    <t>鄧竹君</t>
-  </si>
-  <si>
-    <t>韓紫綾</t>
-  </si>
-  <si>
-    <t>江治峰</t>
-  </si>
-  <si>
-    <t>張素梅</t>
-  </si>
-  <si>
-    <t>王思元</t>
-  </si>
-  <si>
-    <t>周正軒</t>
-  </si>
-  <si>
-    <t>卓呈祈</t>
-  </si>
-  <si>
-    <t>林玉惠</t>
-  </si>
-  <si>
-    <t>沈士和</t>
-  </si>
-  <si>
-    <t>榮彩君</t>
-  </si>
-  <si>
-    <t>林玉萍</t>
-  </si>
-  <si>
-    <t>王勛瑤</t>
-  </si>
-  <si>
-    <t>鍾智宇</t>
-  </si>
-  <si>
-    <t>謝彩鳳/鍾智宇</t>
-  </si>
-  <si>
-    <t>謝彩鳳/張素梅</t>
-  </si>
-  <si>
-    <t>音樂</t>
-  </si>
-  <si>
-    <t>輔導</t>
-  </si>
-  <si>
-    <t>童軍</t>
-  </si>
-  <si>
-    <t>家政</t>
-  </si>
-  <si>
-    <t>健教</t>
-  </si>
-  <si>
-    <t>學校自治</t>
-  </si>
-  <si>
-    <t>農騰虎嘯</t>
-  </si>
-  <si>
-    <t>品味生活</t>
-  </si>
-  <si>
-    <t>體育</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>邱翊睿</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>廖怡然</t>
-  </si>
-  <si>
-    <t>國文</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>數學</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>英文</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>地理</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>歷史</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>公民</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>自然</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>生活科技</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>視覺藝術</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>表演藝術</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>本土語</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>人文風光</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>社團活動</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>風馳電掣</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>全球化</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>資訊科技</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>生物</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>班級</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>謝彩鳳/
+鍾智宇</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>謝彩鳳/
+張素梅</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -714,91 +723,91 @@
   <sheetData>
     <row r="1" spans="1:29" ht="33" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="P1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="W1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="W1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AC1" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -806,74 +815,74 @@
         <v>701</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="O2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="R2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="U2" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z2" s="6"/>
       <c r="AA2" s="6"/>
@@ -885,74 +894,74 @@
         <v>702</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="U3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="6"/>
       <c r="AA3" s="6"/>
@@ -964,73 +973,73 @@
         <v>801</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="O4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="U4" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
       <c r="Z4" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="AA4" s="6"/>
       <c r="AB4" s="6"/>
@@ -1041,73 +1050,73 @@
         <v>802</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="N5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W5" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
       <c r="Z5" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA5" s="6"/>
       <c r="AB5" s="6"/>
@@ -1118,73 +1127,73 @@
         <v>803</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" s="4" t="s">
+      <c r="T6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="U6" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA6" s="6"/>
       <c r="AB6" s="6"/>
@@ -1195,77 +1204,77 @@
         <v>901</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="4"/>
+      <c r="K7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="4" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V7" s="6"/>
       <c r="W7" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="AA7" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1273,77 +1282,77 @@
         <v>902</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" s="4"/>
+      <c r="K8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="4" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="V8" s="7"/>
       <c r="W8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
       <c r="AA8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC8" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC8" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
